--- a/광주_조기축구팀_목록_최근6개월.xlsx
+++ b/광주_조기축구팀_목록_최근6개월.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="축구팀" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="풋살팀(참고)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="축구팀 (통합)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="여성팀(참고)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'축구팀'!$A$1:$M$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'풋살팀(참고)'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'축구팀 (통합)'!$A$1:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'여성팀(참고)'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,24 +468,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>축구팀</t>
+          <t>남성 축구팀</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>12팀 (조기·일요일 오전 8팀, 저녁·오후 4팀)</t>
+          <t>47팀 — 주말 조기 33팀, 평일 조기·오전 5팀, 오후·저녁 9팀</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>풋살팀(참고)</t>
+          <t>여성팀(참고)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>9팀</t>
+          <t>5팀</t>
         </is>
       </c>
     </row>
@@ -496,24 +496,24 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>자료 출처</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>네이버 검색 API (카페글·블로그·웹문서), 검색어 15종 조합 약 14,500건 수집 후 광주광역시·팀 관련 글만 선별</t>
+          <t>① 네이버 카페 '모두의 풋살축구' 모집글  ② 당근 모임 (네이버 웹문서 검색으로 찾은 공개 모임 페이지)  ③ 네이버 블로그</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>최근 활동일</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>카페 글은 작성일이 제공되지 않아 카페 공개 글목록의 글번호-작성일 관계로 추정 (±수일 오차 가능). 블로그는 실제 작성일.</t>
+          <t>카페: 글번호로 추정한 작성일 / 당근: 모임 페이지에 표시된 가장 최근 게시글·가입 날짜 / 블로그: 작성일</t>
         </is>
       </c>
     </row>
@@ -525,19 +525,19 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>경기도 광주·하남·성남 등 타지역 글, 프로구단(광주FC 등)·유소년·여성팀, 6개월 이전 글만 있는 팀</t>
+          <t>경기도 광주 등 타지역, 프로구단, 레슨·강습 모임, 경기 시청·촬영 모임, 6개월 이내 활동 흔적이 없는 모임</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>한계</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>검색에 노출된 팀만 포함되므로 실제 활동 팀 전체가 아님. 연락처는 개인정보라 수록하지 않음 → 링크로 원문 확인</t>
+          <t>같은 팀이 이름을 조금씩 다르게 쓴 경우 중복일 수 있음(예: 일곡FC). 연락처는 수록하지 않았으니 링크에서 확인. 검색에 잡힌 팀만 포함.</t>
         </is>
       </c>
     </row>
@@ -552,22 +552,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,42 +598,42 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>활동시간</t>
+          <t>요일·시간</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>연령대</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>연령대</t>
+          <t>규모</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>실력/리그</t>
+          <t>특징</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>최근 활동일</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>최근 글 날짜</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
-          <t>출처</t>
+          <t>링크 1</t>
         </is>
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
-          <t>링크</t>
+          <t>링크 2</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>백산FC</t>
+          <t>상일FC 조기축구회</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -653,46 +653,50 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>문화근린공원축구장 (문흥동)</t>
+          <t>덕흥동 광신대교 아래 천변 천연잔디구장</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>일 06:00~09:00</t>
+          <t>일 07:00~ (하절기 06:30~)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>37명</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+          <t>25~60대</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 21</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>실력 무관</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2파전 위주</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 (추정)</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2566892</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%83%81%EC%9D%BCfc-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC%ED%9A%8C-ydq443n77bei/</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -700,7 +704,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>어울림FC</t>
+          <t>창무FC</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -710,52 +714,48 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>안청구장 (하남산단 8번로)</t>
+          <t>문화근린공원 축구장</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>일 07:00~11:00 / 목 19:00~21:00</t>
+          <t>토 06:00~09:00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>42명</t>
+          <t>20~40대</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>20~50대</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>당근 멤버 21</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>9/28 용병모집 글도 있음</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28 (추정)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EC%B0%BD%EB%AC%B4fc-v6cukc5sz6hn/</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/haha999/2580705</t>
+          <t>https://www.daangn.com/kr/group/%EC%B0%BD%EB%AC%B4-fc-%ED%86%A0%EC%9A%94%EC%9D%BC-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EC%9D%B8%EC%9B%90%EB%AA%A8%EC%A7%91-qqcatwpg9w6w/</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>한솔FC (한솔축구회)</t>
+          <t>백산FC</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -775,44 +775,48 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>하남연합회 배정 구장 (하남공원·스포츠파크·풍영·보라매)</t>
+          <t>문화근린공원 (청소년수련관 운동장)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>일 오전</t>
+          <t>일 06:00~09:00</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>37명</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>디비전·각종 대회 참가</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1985년 창단, 하남연합회 소속</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 (추정)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
+          <t>당근 모임 + 카페(추정)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EB%B0%B1%EC%82%B0fc-8yxddpthji8z/</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/haha999/2561557</t>
+          <t>https://cafe.naver.com/haha999/2566892</t>
         </is>
       </c>
     </row>
@@ -822,7 +826,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>송화FC</t>
+          <t>어울림FC</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -832,44 +836,48 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>광산구·서구</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>안청구장 (하남산단 8번로)</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>일 07:00~11:00</t>
+          <t>일 07:00~11:00 / 목 19:00~21:00</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>37명</t>
+          <t>20~50대</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>20대 중~30대 후</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>C / K7</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>42명</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12 (추정)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
+          <t>카페(추정) + 당근 모임</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2580705</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/haha999/2518374</t>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%EC%96%B4%EC%9A%B8%EB%A6%BC-%EC%B6%95%EA%B5%AC-4b5m8wv8cupd/</t>
         </is>
       </c>
     </row>
@@ -879,7 +887,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>중흥FC (중흥조기축구회)</t>
+          <t>송원FC (송원고 총동문회)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -889,46 +897,46 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>전대사대부중 운동장 (중흥동, 과거 글 기준)</t>
+          <t>인재교육원·보라매 등 순회 / 목 기아구장</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>일 오전</t>
+          <t>일 07:00~12:00 / 목 18:00~21:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>50명</t>
+          <t>40~60대</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>송원고 동문 클럽</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1980년 창단, '30년 전통' 소개</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07 (추정)</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2515478</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%86%A1%EC%9B%90%EA%B3%A0%EC%B4%9D%EB%8F%99%EB%AC%B8%ED%9A%8C%EC%B6%95%EA%B5%AC%ED%81%B4%EB%9F%BD-%EC%86%A1%EC%9B%90fc-hyowbk85mgav/</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -936,7 +944,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>수완FC</t>
+          <t>화정FC</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -946,46 +954,42 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>안청공원 인조잔디 축구장</t>
+          <t>압촌·대촌 인근</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>일 07:30~12:00</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>20~50대</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>일 오전</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>40~50대</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07 (추정)</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2498119</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%99%94%EC%A0%95fc%EC%97%90%EC%84%9C-40-50%EB%8C%80-%EC%B6%95%EA%B5%AC-%EC%9A%B4%EB%8F%99-%EA%B0%99%EC%9D%B4%ED%95%98%EC%8B%A4-6j1h4srrwg1x/</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -993,7 +997,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>광산FC</t>
+          <t>상암FC</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1003,50 +1007,46 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>서구</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>31사단 인조구장 (오치동)</t>
+          <t>마륵구장</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>일 07:00~11:00 (3파전)</t>
+          <t>일 07:00~11:00</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>30명</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
           <t>20~50대</t>
         </is>
       </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>2002년 창단</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06 (추정)</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2479943</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EC%84%9C%EA%B5%AC-%EC%83%81%EC%95%94fc-wk71uwt2cr2v/</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1082,24 +1082,20 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>블로그 해시태그 #전남광주하남연합회 #하남조기축구회</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 (블로그 작성일)</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>네이버 블로그</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+          <t>블로그</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>https://blog.naver.com/nadaesoo/224412018448</t>
         </is>
       </c>
+      <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1107,62 +1103,58 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>로나FC</t>
+          <t>자크FC</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>저녁/주말</t>
+          <t>조기</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>서구·동구</t>
+          <t>광산구</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>동구다목적체육관 (화) 외</t>
+          <t>소촌동 인재교육원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>화 19:00~22:00 / 일요일</t>
+          <t>일 오전</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>약 60명</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>30대~</t>
-        </is>
-      </c>
+          <t>20대 후~40대 초</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>K6·K7</t>
+          <t>30대 주축</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>광주 서구축구협회 소속, 6/17 용병모집 글도 있음</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 (추정)</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%9E%90%ED%81%ACfc-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-2jxnpauih879/</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/haha999/2522342</t>
+          <t>https://www.daangn.com/kr/group/%EC%9E%90%ED%81%AC-fc-%ED%9A%8C%EC%9B%90-%EB%AA%A8%EC%A7%91-nhaitxwb86ug/</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1164,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>한광FC</t>
+          <t>해오름FC</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>오후</t>
+          <t>조기</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1187,41 +1179,41 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>광덕고 인조잔디구장</t>
+          <t>덕흥구장</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>일 15:00~18:00</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>나이 무관</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>40~50대</t>
+          <t>당근 멤버 40</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>고정 매칭팀 구하는 글</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01 (추정)</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2565180</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%ED%95%B4%EC%98%A4%EB%A6%84fc-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91%ED%95%A9%EB%8B%88%EB%8B%A4-i7e3ofxroq45/</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1229,56 +1221,60 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>퍼즐FC</t>
+          <t>5060 교대 축구</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>저녁</t>
+          <t>조기</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>풍영구장·안청구장</t>
+          <t>광주교대 운동장</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>수 21:00~23:00</t>
+          <t>일 오전</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>20~30명</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+          <t>50~60대</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 30</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>리그 참가</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
+          <t>친목 위주</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29 (추정)</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2581705</t>
-        </is>
-      </c>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/5060-%EA%B5%90%EB%8C%80%EC%97%90%EC%84%9C-%EC%B6%95%EA%B5%AC%ED%95%B4%EC%9A%94-94bt2ru7xmzg/</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1286,72 +1282,2050 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>BIA 축구클럽 (비아)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>안청공원 인조구장</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00 (3파전)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>성인</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%EB%B9%84%EC%95%84fc-%EC%B6%95%EA%B5%AC-%ED%9A%8C%EC%9B%90-%EB%AA%A8%EC%A7%91%ED%95%A9%EB%8B%88%EB%8B%A4-k6axuejwo9m6/</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>FC샤크스</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>광산구 관내 축구장</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>일 오전 (하계 07:00)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>20대 초~40대 초</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>50명</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>K7, 연합회·구 대회</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/fc%EC%83%A4%ED%81%AC%EC%8A%A4-13v54mbef57p/</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>송암FC</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>송원대학교 운동장</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>20~60대</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>약 25명</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%EB%82%A8%EA%B5%AC-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EC%86%A1%EC%95%94fc-j5r2jn3obrdv/</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>RG FC</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>하남스포츠파크 (산정동)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>토 08:00~12:00</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/rg-fc-%EC%B6%95%EA%B5%AC%ED%95%98%EC%8B%A4%EB%B6%84-%EB%8C%80%ED%99%98%EC%98%81%ED%95%A9%EB%8B%88%EB%8B%A4-yathybo98edi/</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>한솔FC (한솔축구회)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>하남연합회 배정 인조구장</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~12:00</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>K7, 1985년 창단</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정) + 당근 모임</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2561557</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%95%9C%EC%86%94fc-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-4c25qm52zmhk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>서구560FC</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>서구</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>일 아침</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%84%9C%EA%B5%AC560fc-tm88xe25wdqg/</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>뉴불FC (New Bull)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>문흥근린공원 축구장</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>토 06:00~09:00</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>20~40대</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 52</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EB%89%B4%EB%B6%88-newbull-fc-vqdp6cu4ucdv/</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>하남FC (하남조기축구회)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>풍영구장·스포츠파크 등</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>일 오전</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>20~30대</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 27</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%95%98%EB%82%A8fc-misn9f4h1soz/</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>다크호스</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>매곡동 공무원연수원 / 담양 수북중 격주</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>일 06:30~11:00 (동계 07:30~)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC%ED%8C%80-%EB%8B%A4%ED%81%AC%ED%98%B8%EC%8A%A4-%EC%9D%BC%EC%9A%94%EC%9D%BC-%EC%98%A4%EC%A0%84-2mf21i7x4rze/</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>신화FC (광산)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>월전공원 인조잔디구장 (평동산단로)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>일 07:30~11:00</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EA%B4%91%EC%82%B0%EA%B5%AC-%EC%8B%A0%ED%99%94fc-qm83uxt79hcq/</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>선운FC</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>광산구 평동 일대</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>일 08:00~</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>20~60대</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>40여 명</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%84%A0%EC%9A%B4fc-%EC%B6%95%EA%B5%AC%ED%8C%80-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-%EC%84%A0%EC%B6%9C%EB%8B%A4%EC%88%98%EB%B3%B4%EC%9C%A0-9xm8ptuw897e/</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>FC베스트</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>문성고</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>20~60대</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/fc%EB%B2%A0%EC%8A%A4%ED%8A%B8-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-gg8v2x1ixk9t/</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>천우FC</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>서구·광산구</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>기아축구장(광천) / 소촌동 공무원연수원 격주</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>일 08:00~11:00</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>약 30명</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%B2%9C%EC%9A%B0fc-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-fxrr67i6jy3x/</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>송화FC</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>광산구·서구</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>20대 중~30대 후</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>37명</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2518374</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>중흥FC (중흥조기축구회)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>전대사대부중 운동장</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>일 오전</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>50명</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>1980년 창단</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2515478</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>용동FC</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>송정동 일대</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>일 07:30~</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%9A%A9%EB%8F%99fc-%EC%9D%BC%EC%9A%94%EC%9D%BC-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-hp4xzghtepi9/</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>일곡FC / 북구 일곡동 조기축구</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>일곡근린공원 운동장</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>토·일 06:00~</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>20~40대</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>당근에 모임 2개 (같은 팀일 수 있음)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%9D%BC%EA%B3%A1fc-%EC%B6%95%EA%B5%AC-s3gv3x8yt3r2/</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EB%B6%81%EA%B5%AC-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-%EC%9D%BC%EA%B3%A1%EB%8F%99-zdbpmfkouwi2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>수완FC</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>안청공원 인조잔디 축구장</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>일 07:30~12:00</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2498119</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>미리내 조기축구회</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>남부대 운동장</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~12:00</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>20~40대</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2002년 결성</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EB%AF%B8%EB%A6%AC%EB%82%B4-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC%ED%9A%8C-%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-jgjvis7xik27/</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>FC맥 (동강대 조기축구회)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>동강대 인조잔디구장</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>상시 모집</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EB%8F%99%EA%B0%95%EB%8C%80-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC%ED%9A%8C-%EC%9D%B8%EC%9B%90%EB%AA%A8%EC%A7%91-%ED%95%A9%EB%8B%88%EB%8B%A4-s1b1akvgoaop/</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>광산FC</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>31사단 인조구장 (오치동)</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>일 07:00~11:00</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>30명</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2479943</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>주월FC</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>일 06:30~11:30</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>20대 중~50대</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>순수 아마추어</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EB%82%A8%EA%B5%AC-%EC%A3%BC%EC%9B%94fc-40%EB%8C%80%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91%EC%A4%91-%EC%84%A0%EC%B6%9C%ED%99%98%EC%98%81-4ktpos5cokc8/</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>진월 화요축구</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>조기(평일)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>진월복합운동장</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>화 07:30~09:30</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 102</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>참여 시 2,000원</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%A7%84%EC%9B%94-%ED%99%94%EC%9A%94%EC%B6%95%EA%B5%AC-bb5m43qob2ky/</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>아침 축구회</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>조기(평일)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>수완동 일대</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>화~토 06:00~07:00, 주말 정식경기</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 48</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>평일은 미니골대, 월회비 1만원</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%92%8D%EC%98%81fc-%EC%95%84%EC%B9%A8-%EC%B6%95%EA%B5%AC%ED%9A%8C-npzeqf9imo26/</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>수요일 조기축구 (보라매)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>조기(평일)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>서구</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>보라매구장 (공항 옆)</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>수 08:00~</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>30대 이상</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%88%98%EC%9A%94%EC%9D%BC-%EC%A1%B0%EA%B8%B0%EC%B6%95%EA%B5%AC-%EB%B3%B4%EB%9D%BC%EB%A7%A4%EA%B5%AC%EC%9E%A5-6zd76y1gv8ev/</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>조기 + 평일 야간</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>동구</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>용산생활체육공원</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>일 오전 / 평일 야간</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>20~40대</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>디비전7, 청장기·협회장기</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%B6%95%EA%B5%AC-%ED%9A%8C%EC%9B%90-%EB%AA%A8%EC%A7%91-u6kftph518dh/</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>광직FC (광주직할시 축구회)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>평일 오전</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>일곡근린공원 축구장</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>평일 09:00~11:30</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>월회비 15,000원</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A7%81fc-qedyfnus4ngh/</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>한광FC</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>오후</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>서구</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>광덕고 인조잔디구장</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>일 15:00~해질 때까지</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>40~50대</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>32명</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정) + 당근 모임</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2565180</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%95%9C%EA%B4%91fc-%EC%B6%95%EA%B5%AC%ED%9A%8C%EC%9B%90%EB%AA%A8%EC%A7%91-%EB%AA%A9-%EC%9D%BC-%EC%A3%BC2%ED%9A%8C-%EC%9A%B4%EB%8F%99-1wm79ajpa6c5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>예향FC</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>주말 낮</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>진월복합구장 등</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>토 12:00~16:00 외</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>약 80명</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>창단 30년+, 북구 소속</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EC%98%88%ED%96%A5fc-%EC%8B%A0%EA%B7%9C%ED%9A%8C%EC%9B%90-%EB%AA%A8%EC%A7%91-%ED%95%A8%EA%BB%98%ED%95%98%EC%8B%A4-%EB%B6%84-jgf131uiu4kp/</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>로나FC</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>저녁/주말</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>서구</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>동구다목적체육관 (화) 외</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>화 19:00~22:00 / 일 주간</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>20~50대</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>약 60명</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>K6·K7·50대리그, 서구축구협회</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임 + 카페(추정)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EC%84%9C%EA%B5%AC%EB%A1%9C%EB%82%98fc-zux7ze4vk5kp/</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2522342</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>아우라FC</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>효천근린공원 축구장</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>목 19:30~22:00</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>11:11 2파전</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%95%84%EC%9A%B0%EB%9D%BCfc-%ED%8C%80%EC%9B%90%EB%AA%A8%EC%A7%91%EC%A4%91-f1gsawhs1f7r/</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>퍼즐FC</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>풍영구장·안청구장</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>수 21:00~23:00</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>20~30명</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>리그 참가</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/haha999/2581705</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>퇴근 후 실내축구 (봉선)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>실내축구장</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>평일 저녁</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%ED%87%B4%EA%B7%BC%ED%9B%84-%EC%8B%A4%EB%82%B4%EC%97%90%EC%84%9C-%EC%B6%95%EA%B5%AC-%ED%95%9C%EC%9E%94-enmgbpcbfque/</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>신화FC (화요 야간)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>동구</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>용산구장</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>화 19:00~</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 34</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>광산 신화FC와 다른 팀일 수 있음</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%8B%A0%ED%99%94fc-9kaivsxqvm9c/</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
           <t>대촌팀</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>저녁</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>남구</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>남구다목적축구장 (진월동)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>수·일 18:30~21:00</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>20~40대</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-12 (추정)</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>카페(추정)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>https://cafe.naver.com/haha999/2518607</t>
         </is>
       </c>
+      <c r="M47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>FC올빼미</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>광산구</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>풍영축구장</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>금 21:00~23:00 / 일 20:00~22:00</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>20세 이상</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>당근 멤버 62</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>당근 모임</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/fc%EC%98%AC%EB%B9%BC%EB%AF%B8-%EA%B8%88-%EC%A0%80%EB%85%819%EC%8B%9C-%EC%9D%BC-%EC%A0%80%EB%85%818%EC%8B%9C-%ED%92%8D%EC%98%81%EA%B5%AC%EC%9E%A5-y7zi6z3854c3/</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M13"/>
+  <autoFilter ref="A1:M48"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1363,20 +3337,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1397,40 +3367,20 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>구장</t>
+          <t>활동</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>활동시간</t>
+          <t>비고</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>최근 활동일</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>연령대</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>실력</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>최근 글 날짜</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>출처</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
@@ -1442,48 +3392,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>이글루FS</t>
+          <t>큐브WFC</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>서구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>스타실내풋살장 (세하동)</t>
+          <t>월·목 19:00~21:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>목 19:00~21:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>20대 후~40대 초</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>C-</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02 (추정)</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2583078</t>
+          <t>여자 신생팀</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EC%97%AC%EC%9E%90-%EC%B6%95%EA%B5%AC%ED%8C%80-%ED%81%90%EB%B8%8C-w-s-t-bt9df83v7t2x/</t>
         </is>
       </c>
     </row>
@@ -1493,48 +3427,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>상지풋살 금요일팀</t>
+          <t>핑클 (Finkl WFC)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>광산구</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>상지풋살장</t>
+          <t>화·목 저녁, 첨단구장</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>금 20:00~22:00</t>
+          <t>여자 아마추어</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>13명</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>20~40대</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-19 (추정)</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2576052</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%EC%97%AC%EC%9E%90-%EC%B6%95%EA%B5%AC%ED%8C%80-%ED%95%91%ED%81%B4-9hdopo67odgi/post/</t>
         </is>
       </c>
     </row>
@@ -1544,48 +3462,28 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>전광WFC</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>베스트풋살장 (풍영정길)</t>
-        </is>
-      </c>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>금 20:00~22:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>30~40대</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>하~중</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-12 (추정)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2571760</t>
+          <t>여자 풋살·축구</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC%EC%97%AC%EC%9E%90%ED%92%8B%EC%82%B4%EC%B6%95%EA%B5%AC-%EC%A0%84%EA%B4%91wfc-vyoffgtdgtaj/</t>
         </is>
       </c>
     </row>
@@ -1595,48 +3493,28 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>바로풋살 수요일팀</t>
+          <t>부키W-FC</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>서구</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>바로풋살장</t>
-        </is>
-      </c>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>수 21:00~23:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>28~40</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>B~C</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28 (추정)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2563070</t>
+          <t>북구 여성축구단</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EB%B6%81%EA%B5%AC%EC%97%AC%EC%84%B1%EC%B6%95%EA%B5%AC%EB%8B%A8-yju9hwzjireg/</t>
         </is>
       </c>
     </row>
@@ -1646,251 +3524,43 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>위너풋살 목요일팀</t>
+          <t>텐션FC</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>위너풋살장 1호점</t>
+          <t>진월복합운동장 풋살장</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>목 21:00~24:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>30대 초~40대 후</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27 (추정)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2562591</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>SANUS</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>상지풋살장</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>목 21:00~23:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-23 (추정)</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2560210</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FC WATT</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>더프라임 풋살장</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>수 20:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>24명</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-15 (추정)</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2555456</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>스타풋살 수요일팀(인조잔디)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>서구</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>스타실내풋살장 (세하동)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>수 19:00~21:00</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>35~45</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12 (추정)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2554068</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>티라노FC</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>서구</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>더프라임 풋살장</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>일 08:00~10:00 (가끔 목 20~22)</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>20~30대</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>C~C-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-14 (추정)</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>모두의 풋살축구 카페</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/haha999/2537266</t>
+          <t>여자 축구·풋살</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.daangn.com/kr/group/%EA%B4%91%EC%A3%BC-%EC%97%AC%EC%9E%90%EC%B6%95%EA%B5%AC-%ED%92%8B%EC%82%B4-%ED%85%90%EC%85%98fc-z4kq6zd551zn/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
